--- a/automated_test/report.xlsx
+++ b/automated_test/report.xlsx
@@ -10,9 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$K$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,25 +29,63 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="16"/>
+      <color rgb="001E293B"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="00111827"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00374151"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00854D0E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,14 +94,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
-        <bgColor rgb="001F2937"/>
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+        <bgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,32 +133,74 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00E2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00E2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00E2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00E2E8F0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,141 +567,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vulnerability Testing Report</t>
+          <t>LegalEase — DAST Security Vulnerability Summary</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Generated At</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-11 14:37:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Report File</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>automated_test\report.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Workbook template ready. Run vulnerability tests to populate findings.</t>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Scope Details:</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>DAST Application Protection Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Audit Database:</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Supabase Cloud API Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Scan Timestamp:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Endpoints Discovered</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Severity Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Severity Level</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Findings Count</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Resolution Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Tests Run</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Immediate Action Required (Hotfix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Resolve within 48 Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Critical Findings</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Resolve in Upcoming Sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Low/Info</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>High Findings</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Medium Findings</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Low Findings</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Informational &amp; Hardening Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Secure Passes</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Complies with Security Benchmarks</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -617,134 +735,685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>endpoint</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>expected_status</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>response_time_ms</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>test_category</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Role Profile</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>HTTP Status</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Expected Rules</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Finding Summary</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Security Remediation Note</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Static Code Scan</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>FILE</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Vulnerable</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>No Secret Exposed</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded api_key String</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded Credentials</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>Found hardcoded connection string/secret in scanner.py line 13</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Static Code Scan</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>FILE</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Vulnerable</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>No Secret Exposed</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded api_key String</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded Credentials</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Found hardcoded connection string/secret in test_backup.py line 4</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Static Code Scan</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>FILE</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Vulnerable</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>No Secret Exposed</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded api_key String</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded Credentials</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Found hardcoded connection string/secret in web\scanner.py line 13</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Static Code Scan</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>FILE</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Vulnerable</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>No Secret Exposed</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded api_key String</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Hardcoded Credentials</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Found hardcoded connection string/secret in web\test_backup.py line 4</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>/process</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>public</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>validated after test run</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Run the DAST workflow to replace this row with real vulnerability results.</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-11 14:37:15</t>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Anonymous</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Secure</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>401 Unauthorized / missing file error</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>AuthN Bypass check without API Token</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>AuthN Bypass</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Request blocked client-side or handled gracefully via server exception guards.</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>RBAC Matrix Access Verification</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>RBAC Matrix</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Standard user token validates permissions correctly.</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Privilege Escalation verification</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>AuthZ / PrivEsc</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>Admin credentials allowed access to system metrics successfully.</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Secure</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>400/500/validation block</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>SQL Injection Detection Probe</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Injection Probes</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Probed /process with SQLi payload: ' OR '1'='1. Sanitized and validation filters successfully block query execution.</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Secure</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>400/500/validation block</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>SQL Injection Detection Probe</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Injection Probes</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>Probed /process with SQLi payload: '; DROP TABLE analyses;--. Sanitized and validation filters successfully block query execution.</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Secure</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>400/500/validation block</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>SQL Injection Detection Probe</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Injection Probes</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Probed /process with SQLi payload: admin'--. Sanitized and validation filters successfully block query execution.</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>/process</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Protected</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>429 Too Many Requests</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Throttling &amp; Burst Validation</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>Sent a burst of 30 requests within 1000ms. Throttling rules restricted throughput to avoid DDOS vulnerability.</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:05:44</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>